--- a/SourceCode/BaocaoTonghop_T2_new.xlsx
+++ b/SourceCode/BaocaoTonghop_T2_new.xlsx
@@ -16,10 +16,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* (#,##0);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* (#,##0);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0.00_);_(* (#,##0.00);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0.00_);_(* -#,##0.00_);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="168" formatCode="_(* #,##0.0_);_(* -#,##0.0_);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -62,7 +64,7 @@
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -119,6 +121,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E3B825"/>
+        <bgColor rgb="00E3B825"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F07A17"/>
+        <bgColor rgb="00F07A17"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="000000FF"/>
         <bgColor rgb="000000FF"/>
       </patternFill>
@@ -142,9 +156,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -190,6 +204,36 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -557,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47" customWidth="1" min="1" max="1"/>
@@ -989,550 +1033,550 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>CP vốn TT 2</t>
+          <t>DT Nguồn vốn</t>
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>-9320.709999999999</v>
+        <v>0</v>
       </c>
       <c r="C11" s="14" t="inlineStr"/>
       <c r="D11" s="14" t="inlineStr"/>
       <c r="E11" s="14" t="inlineStr"/>
       <c r="F11" s="13" t="n">
-        <v>-9320.709999999999</v>
+        <v>0</v>
       </c>
       <c r="G11" s="15" t="inlineStr"/>
       <c r="H11" s="16" t="n">
-        <v>-1071.64</v>
+        <v>0</v>
       </c>
       <c r="I11" s="16" t="n">
-        <v>-598.53</v>
+        <v>0</v>
       </c>
       <c r="J11" s="16" t="n">
-        <v>-1418.44</v>
+        <v>0</v>
       </c>
       <c r="K11" s="16" t="n">
-        <v>-289.27</v>
+        <v>0</v>
       </c>
       <c r="L11" s="16" t="n">
-        <v>-812.4299999999999</v>
+        <v>0</v>
       </c>
       <c r="M11" s="16" t="n">
-        <v>-3751.87</v>
+        <v>0</v>
       </c>
       <c r="N11" s="16" t="n">
-        <v>-1578.01</v>
+        <v>0</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>-9520.190000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>CP vốn CCTG</t>
+          <t>CP vốn TT 2</t>
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>-122820.4</v>
+        <v>-9320.709999999999</v>
       </c>
       <c r="C12" s="14" t="inlineStr"/>
       <c r="D12" s="14" t="inlineStr"/>
       <c r="E12" s="14" t="inlineStr"/>
       <c r="F12" s="13" t="n">
-        <v>-122820.4</v>
+        <v>-9320.709999999999</v>
       </c>
       <c r="G12" s="15" t="inlineStr"/>
       <c r="H12" s="16" t="n">
-        <v>-14121.2</v>
+        <v>-1071.64</v>
       </c>
       <c r="I12" s="16" t="n">
-        <v>-7886.94</v>
+        <v>-598.53</v>
       </c>
       <c r="J12" s="16" t="n">
-        <v>-18691.04</v>
+        <v>-1418.44</v>
       </c>
       <c r="K12" s="16" t="n">
-        <v>-3811.75</v>
+        <v>-289.27</v>
       </c>
       <c r="L12" s="16" t="n">
-        <v>-10705.47</v>
+        <v>-812.4299999999999</v>
       </c>
       <c r="M12" s="16" t="n">
-        <v>-49438.98</v>
+        <v>-3751.87</v>
       </c>
       <c r="N12" s="16" t="n">
-        <v>-20793.61</v>
+        <v>-1578.01</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>-125448.99</v>
+        <v>-9520.190000000001</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>Chi phí thuần hoạt động khác</t>
+          <t>CP vốn TT 1</t>
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>-362.68</v>
+        <v>0</v>
       </c>
       <c r="C13" s="14" t="inlineStr"/>
       <c r="D13" s="14" t="inlineStr"/>
       <c r="E13" s="14" t="inlineStr"/>
       <c r="F13" s="13" t="n">
-        <v>-362.68</v>
+        <v>0</v>
       </c>
       <c r="G13" s="15" t="inlineStr"/>
       <c r="H13" s="16" t="n">
-        <v>-5182.52</v>
+        <v>0</v>
       </c>
       <c r="I13" s="16" t="n">
-        <v>-3282.14</v>
+        <v>0</v>
       </c>
       <c r="J13" s="16" t="n">
-        <v>-6255.03</v>
+        <v>0</v>
       </c>
       <c r="K13" s="16" t="n">
-        <v>-1650.72</v>
+        <v>0</v>
       </c>
       <c r="L13" s="16" t="n">
-        <v>-3229.95</v>
+        <v>0</v>
       </c>
       <c r="M13" s="16" t="n">
-        <v>-16707.18</v>
+        <v>0</v>
       </c>
       <c r="N13" s="16" t="n">
-        <v>-7987.63</v>
+        <v>0</v>
       </c>
       <c r="O13" s="8" t="n">
-        <v>-44295.19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>DT Kinh doanh</t>
+          <t>CP vốn CCTG</t>
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>1.75</v>
+        <v>-122820.4</v>
       </c>
       <c r="C14" s="14" t="inlineStr"/>
       <c r="D14" s="14" t="inlineStr"/>
       <c r="E14" s="14" t="inlineStr"/>
       <c r="F14" s="13" t="n">
-        <v>1.75</v>
+        <v>-122820.4</v>
       </c>
       <c r="G14" s="15" t="inlineStr"/>
       <c r="H14" s="16" t="n">
-        <v>5.45</v>
+        <v>-14121.2</v>
       </c>
       <c r="I14" s="16" t="n">
-        <v>3.39</v>
+        <v>-7886.94</v>
       </c>
       <c r="J14" s="16" t="n">
-        <v>6.69</v>
+        <v>-18691.04</v>
       </c>
       <c r="K14" s="16" t="n">
-        <v>1.76</v>
+        <v>-3811.75</v>
       </c>
       <c r="L14" s="16" t="n">
-        <v>3.34</v>
+        <v>-10705.47</v>
       </c>
       <c r="M14" s="16" t="n">
-        <v>17.36</v>
+        <v>-49438.98</v>
       </c>
       <c r="N14" s="16" t="n">
-        <v>8.59</v>
+        <v>-20793.61</v>
       </c>
       <c r="O14" s="8" t="n">
-        <v>46.57</v>
+        <v>-125448.99</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">CP hoa hồng </t>
+          <t>Chi phí thuần hoạt động khác</t>
         </is>
       </c>
       <c r="B15" s="10" t="n">
-        <v>-186.65</v>
+        <v>-362.68</v>
       </c>
       <c r="C15" s="10" t="inlineStr"/>
       <c r="D15" s="10" t="inlineStr"/>
       <c r="E15" s="10" t="inlineStr"/>
       <c r="F15" s="10" t="n">
-        <v>-186.65</v>
+        <v>-362.68</v>
       </c>
       <c r="G15" s="11" t="inlineStr"/>
       <c r="H15" s="10" t="n">
-        <v>-74.83</v>
+        <v>-5182.52</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>-45.58</v>
+        <v>-3282.14</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>-91.43000000000001</v>
+        <v>-6255.03</v>
       </c>
       <c r="K15" s="10" t="n">
-        <v>-23.36</v>
+        <v>-1650.72</v>
       </c>
       <c r="L15" s="10" t="n">
-        <v>-44.62</v>
+        <v>-3229.95</v>
       </c>
       <c r="M15" s="10" t="n">
-        <v>-238.32</v>
+        <v>-16707.18</v>
       </c>
       <c r="N15" s="10" t="n">
-        <v>-117.24</v>
+        <v>-7987.63</v>
       </c>
       <c r="O15" s="8" t="n">
-        <v>-635.38</v>
+        <v>-44295.19</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">CP thuần KD khác </t>
+          <t>DT Fintech</t>
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>-177.77</v>
+        <v>0</v>
       </c>
       <c r="C16" s="14" t="inlineStr"/>
       <c r="D16" s="14" t="inlineStr"/>
       <c r="E16" s="14" t="inlineStr"/>
       <c r="F16" s="13" t="n">
-        <v>-177.77</v>
+        <v>0</v>
       </c>
       <c r="G16" s="15" t="inlineStr"/>
       <c r="H16" s="16" t="n">
-        <v>-5113.14</v>
+        <v>0</v>
       </c>
       <c r="I16" s="16" t="n">
-        <v>-3239.96</v>
+        <v>0</v>
       </c>
       <c r="J16" s="16" t="n">
-        <v>-6170.29</v>
+        <v>0</v>
       </c>
       <c r="K16" s="16" t="n">
-        <v>-1629.12</v>
+        <v>0</v>
       </c>
       <c r="L16" s="16" t="n">
-        <v>-3188.68</v>
+        <v>0</v>
       </c>
       <c r="M16" s="16" t="n">
-        <v>-16486.22</v>
+        <v>0</v>
       </c>
       <c r="N16" s="16" t="n">
-        <v>-7878.97</v>
+        <v>0</v>
       </c>
       <c r="O16" s="8" t="n">
-        <v>-43706.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>Tổng thu nhập hoạt động</t>
+          <t>DT tiểu thương, cá nhân</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>-123353.8</v>
+        <v>0</v>
       </c>
       <c r="C17" s="14" t="inlineStr"/>
       <c r="D17" s="14" t="inlineStr"/>
       <c r="E17" s="14" t="inlineStr"/>
       <c r="F17" s="13" t="n">
-        <v>-123353.8</v>
+        <v>0</v>
       </c>
       <c r="G17" s="15" t="inlineStr"/>
       <c r="H17" s="16" t="n">
-        <v>57426.19</v>
+        <v>0</v>
       </c>
       <c r="I17" s="16" t="n">
-        <v>31687.67</v>
+        <v>0</v>
       </c>
       <c r="J17" s="16" t="n">
-        <v>76527.42</v>
+        <v>0</v>
       </c>
       <c r="K17" s="16" t="n">
-        <v>15273.47</v>
+        <v>0</v>
       </c>
       <c r="L17" s="16" t="n">
-        <v>44070.28</v>
+        <v>0</v>
       </c>
       <c r="M17" s="16" t="n">
-        <v>202211.65</v>
+        <v>0</v>
       </c>
       <c r="N17" s="16" t="n">
-        <v>84141.41</v>
+        <v>0</v>
       </c>
       <c r="O17" s="8" t="n">
-        <v>511338.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>Tổng chi phí hoạt động</t>
+          <t>DT Kinh doanh</t>
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>-16495.68</v>
+        <v>1.75</v>
       </c>
       <c r="C18" s="14" t="inlineStr"/>
       <c r="D18" s="14" t="inlineStr"/>
       <c r="E18" s="14" t="inlineStr"/>
       <c r="F18" s="13" t="n">
-        <v>-16495.68</v>
+        <v>1.75</v>
       </c>
       <c r="G18" s="15" t="inlineStr"/>
       <c r="H18" s="16" t="n">
-        <v>-10423.56</v>
+        <v>5.45</v>
       </c>
       <c r="I18" s="16" t="n">
-        <v>-6944.91</v>
+        <v>3.39</v>
       </c>
       <c r="J18" s="16" t="n">
-        <v>-15594.06</v>
+        <v>6.69</v>
       </c>
       <c r="K18" s="16" t="n">
-        <v>-3933.76</v>
+        <v>1.76</v>
       </c>
       <c r="L18" s="16" t="n">
-        <v>-6492.52</v>
+        <v>3.34</v>
       </c>
       <c r="M18" s="16" t="n">
-        <v>-30513.8</v>
+        <v>17.36</v>
       </c>
       <c r="N18" s="16" t="n">
-        <v>-17148.94</v>
+        <v>8.59</v>
       </c>
       <c r="O18" s="8" t="n">
-        <v>-91051.56</v>
+        <v>46.57</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>CP nhân viên</t>
+          <t xml:space="preserve">CP hoa hồng </t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>-15074.16</v>
+        <v>-186.65</v>
       </c>
       <c r="C19" s="14" t="inlineStr"/>
       <c r="D19" s="14" t="inlineStr"/>
       <c r="E19" s="14" t="inlineStr"/>
       <c r="F19" s="13" t="n">
-        <v>-15074.16</v>
+        <v>-186.65</v>
       </c>
       <c r="G19" s="15" t="inlineStr"/>
       <c r="H19" s="16" t="n">
-        <v>-9172.66</v>
+        <v>-74.83</v>
       </c>
       <c r="I19" s="16" t="n">
-        <v>-6115.86</v>
+        <v>-45.58</v>
       </c>
       <c r="J19" s="16" t="n">
-        <v>-13799.75</v>
+        <v>-91.43000000000001</v>
       </c>
       <c r="K19" s="16" t="n">
-        <v>-3477.63</v>
+        <v>-23.36</v>
       </c>
       <c r="L19" s="16" t="n">
-        <v>-5715.31</v>
+        <v>-44.62</v>
       </c>
       <c r="M19" s="16" t="n">
-        <v>-26733.39</v>
+        <v>-238.32</v>
       </c>
       <c r="N19" s="16" t="n">
-        <v>-15110.98</v>
+        <v>-117.24</v>
       </c>
       <c r="O19" s="8" t="n">
-        <v>-80125.58</v>
+        <v>-635.38</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>CP quản lý</t>
+          <t xml:space="preserve">CP thuần KD khác </t>
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>-627.11</v>
+        <v>-177.77</v>
       </c>
       <c r="C20" s="14" t="inlineStr"/>
       <c r="D20" s="14" t="inlineStr"/>
       <c r="E20" s="14" t="inlineStr"/>
       <c r="F20" s="13" t="n">
-        <v>-627.11</v>
+        <v>-177.77</v>
       </c>
       <c r="G20" s="15" t="inlineStr"/>
       <c r="H20" s="16" t="n">
-        <v>-356.16</v>
+        <v>-5113.14</v>
       </c>
       <c r="I20" s="16" t="n">
-        <v>-240.73</v>
+        <v>-3239.96</v>
       </c>
       <c r="J20" s="16" t="n">
-        <v>-544.89</v>
+        <v>-6170.29</v>
       </c>
       <c r="K20" s="16" t="n">
-        <v>-136.69</v>
+        <v>-1629.12</v>
       </c>
       <c r="L20" s="16" t="n">
-        <v>-222.91</v>
+        <v>-3188.68</v>
       </c>
       <c r="M20" s="16" t="n">
-        <v>-1026.44</v>
+        <v>-16486.22</v>
       </c>
       <c r="N20" s="16" t="n">
-        <v>-589.8099999999999</v>
+        <v>-7878.97</v>
       </c>
       <c r="O20" s="8" t="n">
-        <v>-3117.65</v>
+        <v>-43706.38</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>CP tài sản</t>
+          <t>CP hợp tác kd tàu (net)</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>-794.41</v>
+        <v>0</v>
       </c>
       <c r="C21" s="14" t="inlineStr"/>
       <c r="D21" s="14" t="inlineStr"/>
       <c r="E21" s="14" t="inlineStr"/>
       <c r="F21" s="13" t="n">
-        <v>-794.41</v>
+        <v>0</v>
       </c>
       <c r="G21" s="15" t="inlineStr"/>
       <c r="H21" s="16" t="n">
-        <v>-894.74</v>
+        <v>0</v>
       </c>
       <c r="I21" s="16" t="n">
-        <v>-588.3200000000001</v>
+        <v>0</v>
       </c>
       <c r="J21" s="16" t="n">
-        <v>-1249.42</v>
+        <v>0</v>
       </c>
       <c r="K21" s="16" t="n">
-        <v>-319.44</v>
+        <v>0</v>
       </c>
       <c r="L21" s="16" t="n">
-        <v>-554.3</v>
+        <v>0</v>
       </c>
       <c r="M21" s="16" t="n">
-        <v>-2753.97</v>
+        <v>0</v>
       </c>
       <c r="N21" s="16" t="n">
-        <v>-1448.15</v>
+        <v>0</v>
       </c>
       <c r="O21" s="8" t="n">
-        <v>-7808.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>Chi phí dự phòng</t>
+          <t>Tổng thu nhập hoạt động</t>
         </is>
       </c>
       <c r="B22" s="10" t="n">
-        <v>-4776</v>
+        <v>-123353.8</v>
       </c>
       <c r="C22" s="10" t="inlineStr"/>
       <c r="D22" s="10" t="inlineStr"/>
       <c r="E22" s="10" t="inlineStr"/>
       <c r="F22" s="10" t="n">
-        <v>-4776</v>
+        <v>-123353.8</v>
       </c>
       <c r="G22" s="11" t="inlineStr"/>
       <c r="H22" s="10" t="n">
-        <v>-40669.97</v>
+        <v>57426.19</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>-23217.68</v>
+        <v>31687.67</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>-42589.76</v>
+        <v>76527.42</v>
       </c>
       <c r="K22" s="10" t="n">
-        <v>-6280.93</v>
+        <v>15273.47</v>
       </c>
       <c r="L22" s="10" t="n">
-        <v>-22274.39</v>
+        <v>44070.28</v>
       </c>
       <c r="M22" s="10" t="n">
-        <v>-110091.54</v>
+        <v>202211.65</v>
       </c>
       <c r="N22" s="10" t="n">
-        <v>-85763.99000000001</v>
+        <v>84141.41</v>
       </c>
       <c r="O22" s="8" t="n">
-        <v>-330888.27</v>
+        <v>511338.1</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>2. Số lượng nhân sự ( Sale Manager )</t>
+          <t>Tổng chi phí hoạt động</t>
         </is>
       </c>
       <c r="B23" s="10" t="n">
-        <v>0</v>
+        <v>-16495.68</v>
       </c>
       <c r="C23" s="10" t="inlineStr"/>
       <c r="D23" s="10" t="inlineStr"/>
       <c r="E23" s="10" t="inlineStr"/>
       <c r="F23" s="10" t="n">
-        <v>0</v>
+        <v>-16495.68</v>
       </c>
       <c r="G23" s="11" t="inlineStr"/>
       <c r="H23" s="10" t="n">
-        <v>0</v>
+        <v>-10423.56</v>
       </c>
       <c r="I23" s="10" t="n">
-        <v>0</v>
+        <v>-6944.91</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>0</v>
+        <v>-15594.06</v>
       </c>
       <c r="K23" s="10" t="n">
-        <v>0</v>
+        <v>-3933.76</v>
       </c>
       <c r="L23" s="10" t="n">
-        <v>0</v>
+        <v>-6492.52</v>
       </c>
       <c r="M23" s="10" t="n">
-        <v>0</v>
+        <v>-30513.8</v>
       </c>
       <c r="N23" s="10" t="n">
-        <v>0</v>
+        <v>-17148.94</v>
       </c>
       <c r="O23" s="8" t="n">
-        <v>0</v>
+        <v>-91051.56</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>CIR (%)</t>
+          <t>CP thuế, phí</t>
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C24" s="14" t="inlineStr"/>
       <c r="D24" s="14" t="inlineStr"/>
       <c r="E24" s="14" t="inlineStr"/>
       <c r="F24" s="13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G24" s="15" t="inlineStr"/>
       <c r="H24" s="16" t="n">
@@ -1563,123 +1607,398 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Margin (%)</t>
+          <t>CP nhân viên</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>-0</v>
+        <v>-15074.16</v>
       </c>
       <c r="C25" s="14" t="inlineStr"/>
       <c r="D25" s="14" t="inlineStr"/>
       <c r="E25" s="14" t="inlineStr"/>
       <c r="F25" s="13" t="n">
-        <v>-0</v>
+        <v>-15074.16</v>
       </c>
       <c r="G25" s="15" t="inlineStr"/>
       <c r="H25" s="16" t="n">
-        <v>0</v>
+        <v>-9172.66</v>
       </c>
       <c r="I25" s="16" t="n">
-        <v>0</v>
+        <v>-6115.86</v>
       </c>
       <c r="J25" s="16" t="n">
-        <v>0</v>
+        <v>-13799.75</v>
       </c>
       <c r="K25" s="16" t="n">
-        <v>0</v>
+        <v>-3477.63</v>
       </c>
       <c r="L25" s="16" t="n">
-        <v>0</v>
+        <v>-5715.31</v>
       </c>
       <c r="M25" s="16" t="n">
-        <v>0</v>
+        <v>-26733.39</v>
       </c>
       <c r="N25" s="16" t="n">
-        <v>-0</v>
+        <v>-15110.98</v>
       </c>
       <c r="O25" s="8" t="n">
-        <v>0</v>
+        <v>-80125.58</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Hiệu suất trên/vốn (%)</t>
+          <t>CP quản lý</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>-0</v>
+        <v>-627.11</v>
       </c>
       <c r="C26" s="14" t="inlineStr"/>
       <c r="D26" s="14" t="inlineStr"/>
       <c r="E26" s="14" t="inlineStr"/>
       <c r="F26" s="13" t="n">
-        <v>-0</v>
+        <v>-627.11</v>
       </c>
       <c r="G26" s="15" t="inlineStr"/>
       <c r="H26" s="16" t="n">
-        <v>0</v>
+        <v>-356.16</v>
       </c>
       <c r="I26" s="16" t="n">
-        <v>0</v>
+        <v>-240.73</v>
       </c>
       <c r="J26" s="16" t="n">
-        <v>0</v>
+        <v>-544.89</v>
       </c>
       <c r="K26" s="16" t="n">
-        <v>0</v>
+        <v>-136.69</v>
       </c>
       <c r="L26" s="16" t="n">
-        <v>0</v>
+        <v>-222.91</v>
       </c>
       <c r="M26" s="16" t="n">
-        <v>0</v>
+        <v>-1026.44</v>
       </c>
       <c r="N26" s="16" t="n">
-        <v>-0</v>
+        <v>-589.8099999999999</v>
       </c>
       <c r="O26" s="8" t="n">
-        <v>0</v>
+        <v>-3117.65</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Hiệu suất BQ/ Nhân sự</t>
+          <t>CP tài sản</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>-1954.4</v>
+        <v>-794.41</v>
       </c>
       <c r="C27" s="14" t="inlineStr"/>
       <c r="D27" s="14" t="inlineStr"/>
       <c r="E27" s="14" t="inlineStr"/>
       <c r="F27" s="13" t="n">
-        <v>-1954.4</v>
+        <v>-794.41</v>
       </c>
       <c r="G27" s="15" t="inlineStr"/>
       <c r="H27" s="16" t="n">
+        <v>-894.74</v>
+      </c>
+      <c r="I27" s="16" t="n">
+        <v>-588.3200000000001</v>
+      </c>
+      <c r="J27" s="16" t="n">
+        <v>-1249.42</v>
+      </c>
+      <c r="K27" s="16" t="n">
+        <v>-319.44</v>
+      </c>
+      <c r="L27" s="16" t="n">
+        <v>-554.3</v>
+      </c>
+      <c r="M27" s="16" t="n">
+        <v>-2753.97</v>
+      </c>
+      <c r="N27" s="16" t="n">
+        <v>-1448.15</v>
+      </c>
+      <c r="O27" s="8" t="n">
+        <v>-7808.33</v>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>Chi phí dự phòng</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="n">
+        <v>-4776</v>
+      </c>
+      <c r="C28" s="10" t="inlineStr"/>
+      <c r="D28" s="10" t="inlineStr"/>
+      <c r="E28" s="10" t="inlineStr"/>
+      <c r="F28" s="10" t="n">
+        <v>-4776</v>
+      </c>
+      <c r="G28" s="11" t="inlineStr"/>
+      <c r="H28" s="10" t="n">
+        <v>-40669.97</v>
+      </c>
+      <c r="I28" s="10" t="n">
+        <v>-23217.68</v>
+      </c>
+      <c r="J28" s="10" t="n">
+        <v>-42589.76</v>
+      </c>
+      <c r="K28" s="10" t="n">
+        <v>-6280.93</v>
+      </c>
+      <c r="L28" s="10" t="n">
+        <v>-22274.39</v>
+      </c>
+      <c r="M28" s="10" t="n">
+        <v>-110091.54</v>
+      </c>
+      <c r="N28" s="10" t="n">
+        <v>-85763.99000000001</v>
+      </c>
+      <c r="O28" s="8" t="n">
+        <v>-330888.27</v>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>2. Số lượng nhân sự ( Sale Manager )</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr"/>
+      <c r="C29" s="14" t="inlineStr"/>
+      <c r="D29" s="14" t="inlineStr"/>
+      <c r="E29" s="14" t="inlineStr"/>
+      <c r="F29" s="18" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="G29" s="15" t="inlineStr"/>
+      <c r="H29" s="17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I29" s="17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J29" s="17" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K29" s="17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L29" s="17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M29" s="17" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N29" s="17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O29" s="19" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>3. Chỉ số tài chính</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr"/>
+      <c r="C30" s="14" t="inlineStr"/>
+      <c r="D30" s="14" t="inlineStr"/>
+      <c r="E30" s="14" t="inlineStr"/>
+      <c r="F30" s="21" t="inlineStr"/>
+      <c r="G30" s="15" t="inlineStr"/>
+      <c r="H30" s="21" t="inlineStr"/>
+      <c r="I30" s="21" t="inlineStr"/>
+      <c r="J30" s="21" t="inlineStr"/>
+      <c r="K30" s="21" t="inlineStr"/>
+      <c r="L30" s="21" t="inlineStr"/>
+      <c r="M30" s="21" t="inlineStr"/>
+      <c r="N30" s="21" t="inlineStr"/>
+      <c r="O30" s="22" t="inlineStr"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>CIR (%)</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr"/>
+      <c r="C31" s="23" t="inlineStr"/>
+      <c r="D31" s="23" t="inlineStr"/>
+      <c r="E31" s="23" t="inlineStr"/>
+      <c r="F31" s="24" t="n">
+        <v>-13.37</v>
+      </c>
+      <c r="G31" s="15" t="inlineStr"/>
+      <c r="H31" s="24" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="I31" s="24" t="n">
+        <v>21.92</v>
+      </c>
+      <c r="J31" s="24" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="K31" s="24" t="n">
+        <v>25.76</v>
+      </c>
+      <c r="L31" s="24" t="n">
+        <v>14.73</v>
+      </c>
+      <c r="M31" s="24" t="n">
+        <v>15.09</v>
+      </c>
+      <c r="N31" s="24" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="O31" s="8" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>Margin (%)</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr"/>
+      <c r="C32" s="23" t="inlineStr"/>
+      <c r="D32" s="23" t="inlineStr"/>
+      <c r="E32" s="23" t="inlineStr"/>
+      <c r="F32" s="25" t="n">
+        <v>-1580.3</v>
+      </c>
+      <c r="G32" s="15" t="inlineStr"/>
+      <c r="H32" s="25" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="I32" s="25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J32" s="25" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="K32" s="25" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="L32" s="25" t="n">
+        <v>26</v>
+      </c>
+      <c r="M32" s="25" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="N32" s="25" t="n">
+        <v>-16.4</v>
+      </c>
+      <c r="O32" s="8" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Hiệu suất trên/vốn (%)</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr"/>
+      <c r="C33" s="23" t="inlineStr"/>
+      <c r="D33" s="23" t="inlineStr"/>
+      <c r="E33" s="23" t="inlineStr"/>
+      <c r="F33" s="25" t="n">
+        <v>-109.4</v>
+      </c>
+      <c r="G33" s="15" t="inlineStr"/>
+      <c r="H33" s="25" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="I33" s="25" t="n">
+        <v>18</v>
+      </c>
+      <c r="J33" s="25" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="K33" s="25" t="n">
+        <v>123.4</v>
+      </c>
+      <c r="L33" s="25" t="n">
+        <v>132.9</v>
+      </c>
+      <c r="M33" s="25" t="n">
+        <v>115.8</v>
+      </c>
+      <c r="N33" s="25" t="n">
+        <v>-83.90000000000001</v>
+      </c>
+      <c r="O33" s="8" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Hiệu suất BQ/ Nhân sự</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr"/>
+      <c r="C34" s="23" t="inlineStr"/>
+      <c r="D34" s="23" t="inlineStr"/>
+      <c r="E34" s="23" t="inlineStr"/>
+      <c r="F34" s="14" t="n">
+        <v>-1954.4</v>
+      </c>
+      <c r="G34" s="15" t="inlineStr"/>
+      <c r="H34" s="14" t="n">
         <v>791.58</v>
       </c>
-      <c r="I27" s="16" t="n">
+      <c r="I34" s="14" t="n">
         <v>217.87</v>
       </c>
-      <c r="J27" s="16" t="n">
+      <c r="J34" s="14" t="n">
         <v>833.8</v>
       </c>
-      <c r="K27" s="16" t="n">
+      <c r="K34" s="14" t="n">
         <v>1011.75</v>
       </c>
-      <c r="L27" s="16" t="n">
+      <c r="L34" s="14" t="n">
         <v>3060.67</v>
       </c>
-      <c r="M27" s="16" t="n">
+      <c r="M34" s="14" t="n">
         <v>5600.57</v>
       </c>
-      <c r="N27" s="16" t="n">
+      <c r="N34" s="14" t="n">
         <v>-1173.22</v>
       </c>
-      <c r="O27" s="8" t="n">
+      <c r="O34" s="26" t="n">
         <v>10343.03</v>
       </c>
     </row>
